--- a/artfynd/S 542-2025 artfynd.xlsx
+++ b/artfynd/S 542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343659</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228985</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228987</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343631</t>
         </is>
       </c>
     </row>
@@ -1303,6 +1333,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343603</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343611</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343632</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343640</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343657</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343676</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343678</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343629</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343656</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343625</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343605</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2523,6 +2613,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343606</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2624,6 +2719,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343618</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,6 +2825,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343635</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2826,6 +2931,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343637</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2927,6 +3037,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343641</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,6 +3143,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343647</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343658</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3230,6 +3355,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343667</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3331,6 +3461,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343599</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3432,6 +3567,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343601</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3533,6 +3673,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343623</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3634,6 +3779,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343645</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3735,8 +3885,45 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>